--- a/sample/kinmu_sample.xlsx
+++ b/sample/kinmu_sample.xlsx
@@ -3,12 +3,13 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1E74301-55C1-BE4E-AF12-A74F0F23FF1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62E9D422-6047-D44F-9E28-B2509A82054E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="21740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="職員マスタ" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="93">
   <si>
     <t>年</t>
     <rPh sb="0" eb="1">
@@ -461,6 +462,78 @@
   <si>
     <t>P（作業療法士）</t>
     <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>職員ID</t>
+  </si>
+  <si>
+    <t>表示名</t>
+  </si>
+  <si>
+    <t>病棟</t>
+  </si>
+  <si>
+    <t>専従</t>
+  </si>
+  <si>
+    <t>専任</t>
+  </si>
+  <si>
+    <t>作業療法士</t>
+  </si>
+  <si>
+    <t>在籍</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>○</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>O</t>
+  </si>
+  <si>
+    <t>P</t>
   </si>
 </sst>
 </file>
@@ -807,7 +880,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -881,6 +954,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -901,18 +986,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1499,8 +1573,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:45" ht="38">
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1508,39 +1582,39 @@
       <c r="F1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="32"/>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="32"/>
-      <c r="R1" s="32"/>
-      <c r="S1" s="32"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="32"/>
-      <c r="V1" s="32"/>
-      <c r="W1" s="32"/>
-      <c r="X1" s="32"/>
-      <c r="Y1" s="32"/>
-      <c r="Z1" s="32"/>
-      <c r="AA1" s="32"/>
-      <c r="AB1" s="32"/>
-      <c r="AC1" s="32"/>
-      <c r="AD1" s="32"/>
-      <c r="AE1" s="32"/>
-      <c r="AF1" s="32"/>
-      <c r="AG1" s="33"/>
-      <c r="AQ1" s="34" t="s">
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
+      <c r="N1" s="36"/>
+      <c r="O1" s="36"/>
+      <c r="P1" s="36"/>
+      <c r="Q1" s="36"/>
+      <c r="R1" s="36"/>
+      <c r="S1" s="36"/>
+      <c r="T1" s="36"/>
+      <c r="U1" s="36"/>
+      <c r="V1" s="36"/>
+      <c r="W1" s="36"/>
+      <c r="X1" s="36"/>
+      <c r="Y1" s="36"/>
+      <c r="Z1" s="36"/>
+      <c r="AA1" s="36"/>
+      <c r="AB1" s="36"/>
+      <c r="AC1" s="36"/>
+      <c r="AD1" s="36"/>
+      <c r="AE1" s="36"/>
+      <c r="AF1" s="36"/>
+      <c r="AG1" s="37"/>
+      <c r="AQ1" s="38" t="s">
         <v>50</v>
       </c>
-      <c r="AR1" s="34"/>
-      <c r="AS1" s="34"/>
+      <c r="AR1" s="38"/>
+      <c r="AS1" s="38"/>
     </row>
     <row r="2" spans="1:45">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="39" t="s">
         <v>51</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -1655,16 +1729,16 @@
       <c r="AN2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="AQ2" s="34" t="s">
+      <c r="AQ2" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="AR2" s="34"/>
+      <c r="AR2" s="38"/>
       <c r="AS2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:45" ht="24" customHeight="1" thickBot="1">
-      <c r="A3" s="36"/>
+      <c r="A3" s="40"/>
       <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
@@ -1846,7 +1920,7 @@
       </c>
     </row>
     <row r="5" spans="1:45">
-      <c r="A5" s="30"/>
+      <c r="A5" s="32"/>
       <c r="B5" s="11" t="s">
         <v>25</v>
       </c>
@@ -1999,7 +2073,7 @@
       </c>
     </row>
     <row r="7" spans="1:45">
-      <c r="A7" s="37"/>
+      <c r="A7" s="30"/>
       <c r="B7" s="11" t="s">
         <v>25</v>
       </c>
@@ -2153,7 +2227,7 @@
       </c>
     </row>
     <row r="9" spans="1:45">
-      <c r="A9" s="37"/>
+      <c r="A9" s="30"/>
       <c r="B9" s="11" t="s">
         <v>25</v>
       </c>
@@ -2293,7 +2367,7 @@
       </c>
     </row>
     <row r="11" spans="1:45">
-      <c r="A11" s="37"/>
+      <c r="A11" s="30"/>
       <c r="B11" s="11" t="s">
         <v>25</v>
       </c>
@@ -2630,7 +2704,7 @@
       </c>
     </row>
     <row r="15" spans="1:45" ht="19" thickBot="1">
-      <c r="A15" s="37"/>
+      <c r="A15" s="30"/>
       <c r="B15" s="11" t="s">
         <v>25</v>
       </c>
@@ -2768,7 +2842,7 @@
       </c>
     </row>
     <row r="17" spans="1:42">
-      <c r="A17" s="37"/>
+      <c r="A17" s="30"/>
       <c r="B17" s="11" t="s">
         <v>25</v>
       </c>
@@ -2887,7 +2961,7 @@
       <c r="AP18" s="12"/>
     </row>
     <row r="19" spans="1:42">
-      <c r="A19" s="37"/>
+      <c r="A19" s="30"/>
       <c r="B19" s="2" t="s">
         <v>25</v>
       </c>
@@ -3005,7 +3079,7 @@
       </c>
     </row>
     <row r="21" spans="1:42">
-      <c r="A21" s="37"/>
+      <c r="A21" s="30"/>
       <c r="B21" s="2" t="s">
         <v>25</v>
       </c>
@@ -3125,7 +3199,7 @@
       <c r="AP22" s="21"/>
     </row>
     <row r="23" spans="1:42">
-      <c r="A23" s="30"/>
+      <c r="A23" s="32"/>
       <c r="B23" s="2" t="s">
         <v>25</v>
       </c>
@@ -3237,7 +3311,7 @@
       <c r="AP24" s="21"/>
     </row>
     <row r="25" spans="1:42">
-      <c r="A25" s="30"/>
+      <c r="A25" s="32"/>
       <c r="B25" s="2" t="s">
         <v>25</v>
       </c>
@@ -3354,7 +3428,7 @@
       </c>
     </row>
     <row r="27" spans="1:42">
-      <c r="A27" s="30"/>
+      <c r="A27" s="32"/>
       <c r="B27" s="2" t="s">
         <v>25</v>
       </c>
@@ -3411,7 +3485,7 @@
       <c r="AG27" s="11"/>
     </row>
     <row r="28" spans="1:42">
-      <c r="A28" s="38"/>
+      <c r="A28" s="33"/>
       <c r="B28" s="22" t="s">
         <v>48</v>
       </c>
@@ -3541,7 +3615,7 @@
       </c>
     </row>
     <row r="29" spans="1:42">
-      <c r="A29" s="39"/>
+      <c r="A29" s="34"/>
       <c r="B29" s="23"/>
       <c r="C29" s="23"/>
       <c r="D29" s="23"/>
@@ -3649,7 +3723,7 @@
       </c>
     </row>
     <row r="31" spans="1:42">
-      <c r="A31" s="37"/>
+      <c r="A31" s="30"/>
       <c r="B31" s="2" t="s">
         <v>25</v>
       </c>
@@ -3769,7 +3843,7 @@
       </c>
     </row>
     <row r="33" spans="1:38">
-      <c r="A33" s="37"/>
+      <c r="A33" s="30"/>
       <c r="B33" s="2" t="s">
         <v>25</v>
       </c>
@@ -3881,7 +3955,7 @@
       </c>
     </row>
     <row r="35" spans="1:38">
-      <c r="A35" s="37"/>
+      <c r="A35" s="30"/>
       <c r="B35" s="2" t="s">
         <v>25</v>
       </c>
@@ -3928,7 +4002,7 @@
       </c>
     </row>
     <row r="36" spans="1:38">
-      <c r="A36" s="40" t="s">
+      <c r="A36" s="31" t="s">
         <v>67</v>
       </c>
       <c r="B36" s="2" t="s">
@@ -3987,7 +4061,7 @@
       </c>
     </row>
     <row r="37" spans="1:38">
-      <c r="A37" s="30"/>
+      <c r="A37" s="32"/>
       <c r="B37" s="2" t="s">
         <v>25</v>
       </c>
@@ -4028,7 +4102,7 @@
       <c r="AG37" s="11"/>
     </row>
     <row r="38" spans="1:38">
-      <c r="A38" s="40" t="s">
+      <c r="A38" s="31" t="s">
         <v>68</v>
       </c>
       <c r="B38" s="2" t="s">
@@ -4087,7 +4161,7 @@
       </c>
     </row>
     <row r="39" spans="1:38">
-      <c r="A39" s="30"/>
+      <c r="A39" s="32"/>
       <c r="B39" s="2" t="s">
         <v>25</v>
       </c>
@@ -4424,21 +4498,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A27"/>
     <mergeCell ref="A28:A29"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="B1:C1"/>
@@ -4446,6 +4505,21 @@
     <mergeCell ref="AQ1:AS1"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="AQ2:AR2"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A32:A33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="A30:A31"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <conditionalFormatting sqref="A3:AH3 C29:AG39">
@@ -4618,4 +4692,328 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D95B11FD-6698-404B-883D-47B8F67C319F}">
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="41" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="41" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" s="41" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="41" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" s="41" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" s="41" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1" s="41" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="41" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" s="41" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" s="41">
+        <v>1</v>
+      </c>
+      <c r="D2" s="41" t="s">
+        <v>77</v>
+      </c>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="41" t="s">
+        <v>78</v>
+      </c>
+      <c r="B3" s="41" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" s="41">
+        <v>1</v>
+      </c>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="41" t="s">
+        <v>79</v>
+      </c>
+      <c r="B4" s="41" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="41">
+        <v>1</v>
+      </c>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="41" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" s="41" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" s="41">
+        <v>1</v>
+      </c>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41" t="s">
+        <v>77</v>
+      </c>
+      <c r="G5" s="41" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="41" t="s">
+        <v>81</v>
+      </c>
+      <c r="B6" s="41" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6" s="41">
+        <v>2</v>
+      </c>
+      <c r="D6" s="41" t="s">
+        <v>77</v>
+      </c>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="41" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" s="41" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7" s="41">
+        <v>2</v>
+      </c>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41" t="s">
+        <v>77</v>
+      </c>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="C8" s="41">
+        <v>2</v>
+      </c>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="41" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" s="41" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" s="41">
+        <v>2</v>
+      </c>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="41" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" s="41" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" s="41">
+        <v>2</v>
+      </c>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="41" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="41" t="s">
+        <v>86</v>
+      </c>
+      <c r="B11" s="41" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" s="41">
+        <v>2</v>
+      </c>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="B12" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" s="41">
+        <v>2</v>
+      </c>
+      <c r="D12" s="41"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="41" t="s">
+        <v>77</v>
+      </c>
+      <c r="G12" s="41" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="41" t="s">
+        <v>88</v>
+      </c>
+      <c r="B13" s="41" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" s="41">
+        <v>3</v>
+      </c>
+      <c r="D13" s="41" t="s">
+        <v>77</v>
+      </c>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="41" t="s">
+        <v>89</v>
+      </c>
+      <c r="B14" s="41" t="s">
+        <v>89</v>
+      </c>
+      <c r="C14" s="41">
+        <v>3</v>
+      </c>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41" t="s">
+        <v>77</v>
+      </c>
+      <c r="F14" s="41"/>
+      <c r="G14" s="41" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="41" t="s">
+        <v>90</v>
+      </c>
+      <c r="B15" s="41" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" s="41">
+        <v>3</v>
+      </c>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="41" t="s">
+        <v>91</v>
+      </c>
+      <c r="B16" s="41" t="s">
+        <v>91</v>
+      </c>
+      <c r="C16" s="41">
+        <v>3</v>
+      </c>
+      <c r="D16" s="41"/>
+      <c r="E16" s="41"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="41" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="41" t="s">
+        <v>92</v>
+      </c>
+      <c r="B17" s="41" t="s">
+        <v>92</v>
+      </c>
+      <c r="C17" s="41">
+        <v>3</v>
+      </c>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41" t="s">
+        <v>77</v>
+      </c>
+      <c r="G17" s="41" t="s">
+        <v>77</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>